--- a/dietitian_forms/001_ideal_weight_information_form--dietitian_forms.xlsx
+++ b/dietitian_forms/001_ideal_weight_information_form--dietitian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -883,17 +883,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ideal_weight_units_choices</t>
+          <t>ideal_body_mass_index_range_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kilograms</t>
+          <t>&lt;18.5_to_&lt;_25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kilograms</t>
+          <t>&lt;18.5 to &lt; 25</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>&lt;18.5_to_&lt;_25</t>
+          <t>25_to_&lt;_30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>&lt;18.5 to &lt; 25</t>
+          <t>25 to &lt; 30</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25_to_&lt;_30</t>
+          <t>30_to_&lt;_35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25 to &lt; 30</t>
+          <t>30 to &lt; 35</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30_to_&lt;_35</t>
+          <t>35_to_&lt;_40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>30 to &lt; 35</t>
+          <t>35 to &lt; 40</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>35_to_&lt;_40</t>
+          <t>40_to_&lt;_45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>35 to &lt; 40</t>
+          <t>40 to &lt; 45</t>
         </is>
       </c>
     </row>
@@ -973,29 +973,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>40_to_&lt;_45</t>
+          <t>45_or_above</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>40 to &lt; 45</t>
+          <t>45 or above</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ideal_body_mass_index_range_choices</t>
+          <t>gender_identity_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>45_or_above</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>45 or above</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
     </row>
@@ -1041,27 +1041,10 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>non-binary</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
-        <is>
-          <t>Non-Binary</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>gender_identity_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
